--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aspenau-my.sharepoint.com/personal/cherie_sun_aspenpharmacare_com_au/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F065D415-737B-491E-8BC3-809BB6FFD4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{F065D415-737B-491E-8BC3-809BB6FFD4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{177A84A5-C4E7-465E-8D52-E1A0B6940893}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>numberOfUnits</t>
   </si>
   <si>
-    <t>EarningsRateID</t>
-  </si>
-  <si>
     <t>4ffcf37b-b8cd-4a2d-9d72-746919629be9</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>3d54dcc7-9457-4dce-9a2f-ee9be4cc87db</t>
+  </si>
+  <si>
+    <t>earningsRateID</t>
   </si>
 </sst>
 </file>
@@ -120,6 +120,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,21 +461,21 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aspenau-my.sharepoint.com/personal/cherie_sun_aspenpharmacare_com_au/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{F065D415-737B-491E-8BC3-809BB6FFD4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{177A84A5-C4E7-465E-8D52-E1A0B6940893}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5FC1CD-CAE1-44DE-A207-D64B1500613C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>numberOfUnits</t>
   </si>
   <si>
-    <t>4ffcf37b-b8cd-4a2d-9d72-746919629be9</t>
-  </si>
-  <si>
     <t>2026-05-25T00:00:00</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>earningsRateID</t>
+  </si>
+  <si>
+    <t>a157b547-096a-4c5e-9b31-ad908646a9cb</t>
   </si>
 </sst>
 </file>
@@ -120,10 +120,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -461,24 +457,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5FC1CD-CAE1-44DE-A207-D64B1500613C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B07C9E8-32AC-489B-A307-6AC20CE171E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>numberOfUnits</t>
   </si>
   <si>
-    <t>2026-05-25T00:00:00</t>
-  </si>
-  <si>
     <t>3d54dcc7-9457-4dce-9a2f-ee9be4cc87db</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>a157b547-096a-4c5e-9b31-ad908646a9cb</t>
+  </si>
+  <si>
+    <t>2026-05-24T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -457,21 +457,21 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B07C9E8-32AC-489B-A307-6AC20CE171E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810B4D1C-BE6F-4465-9BF1-22FBF073155F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <t>a157b547-096a-4c5e-9b31-ad908646a9cb</t>
   </si>
   <si>
-    <t>2026-05-24T00:00:00</t>
+    <t>2026-05-25T00:00:00</t>
   </si>
 </sst>
 </file>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810B4D1C-BE6F-4465-9BF1-22FBF073155F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6B3F68-4358-4998-A4AE-4B540A0411CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <t>a157b547-096a-4c5e-9b31-ad908646a9cb</t>
   </si>
   <si>
-    <t>2026-05-25T00:00:00</t>
+    <t>2026-05-24T00:00:00</t>
   </si>
 </sst>
 </file>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6B3F68-4358-4998-A4AE-4B540A0411CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41E3C2-233E-48E0-A544-484D65E60ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>employeeID</t>
   </si>
@@ -59,7 +59,13 @@
     <t>a157b547-096a-4c5e-9b31-ad908646a9cb</t>
   </si>
   <si>
-    <t>2026-05-24T00:00:00</t>
+    <t>payrollCalendarID</t>
+  </si>
+  <si>
+    <t>cb4913a8-82dc-4d48-ba55-b0d8567f29be</t>
+  </si>
+  <si>
+    <t>2026-05-26T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -439,14 +445,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D3DF93-7FF5-4627-8449-A806EF56857A}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,19 +466,25 @@
       <c r="D1" t="s">
         <v>4</v>
       </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41E3C2-233E-48E0-A544-484D65E60ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7CA84C-FC79-4AE7-AE1D-9A3B9868CE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -59,13 +59,13 @@
     <t>a157b547-096a-4c5e-9b31-ad908646a9cb</t>
   </si>
   <si>
-    <t>payrollCalendarID</t>
-  </si>
-  <si>
-    <t>cb4913a8-82dc-4d48-ba55-b0d8567f29be</t>
-  </si>
-  <si>
     <t>2026-05-26T00:00:00</t>
+  </si>
+  <si>
+    <t>payrollType</t>
+  </si>
+  <si>
+    <t>Weekly</t>
   </si>
 </sst>
 </file>
@@ -449,8 +449,9 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.44140625" customWidth="1"/>
-    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="42.44140625" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -461,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -475,16 +476,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7CA84C-FC79-4AE7-AE1D-9A3B9868CE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4AAD6E-18CC-4D3B-BC4B-12F68473D09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -445,47 +445,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D3DF93-7FF5-4627-8449-A806EF56857A}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="42.44140625" customWidth="1"/>
-    <col min="6" max="6" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4AAD6E-18CC-4D3B-BC4B-12F68473D09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5F059-F0A6-4E3E-B4B6-504173458C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>employeeID</t>
   </si>
@@ -66,13 +66,19 @@
   </si>
   <si>
     <t>Weekly</t>
+  </si>
+  <si>
+    <t>3747f42a-4cda-40c6-8e8f-896cd931f557</t>
+  </si>
+  <si>
+    <t>2026-05-27T00:00:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +90,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -445,9 +457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D3DF93-7FF5-4627-8449-A806EF56857A}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -487,7 +500,25 @@
         <v>8</v>
       </c>
     </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5F059-F0A6-4E3E-B4B6-504173458C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555A876E-4085-4A0D-A3A4-EEDACE354122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
   <sheets>
     <sheet name="TestTS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>employeeID</t>
   </si>
@@ -50,9 +50,6 @@
     <t>numberOfUnits</t>
   </si>
   <si>
-    <t>3d54dcc7-9457-4dce-9a2f-ee9be4cc87db</t>
-  </si>
-  <si>
     <t>earningsRateID</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
   </si>
   <si>
     <t>3747f42a-4cda-40c6-8e8f-896cd931f557</t>
-  </si>
-  <si>
-    <t>2026-05-27T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -457,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D3DF93-7FF5-4627-8449-A806EF56857A}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -471,10 +465,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -485,36 +479,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="F2">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555A876E-4085-4A0D-A3A4-EEDACE354122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B273B15B-3377-4A72-81F2-3018A1CEE6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Weekly</t>
   </si>
   <si>
-    <t>3747f42a-4cda-40c6-8e8f-896cd931f557</t>
+    <t>3d54dcc7-9457-4dce-9a2f-ee9be4cc87db</t>
   </si>
 </sst>
 </file>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B273B15B-3377-4A72-81F2-3018A1CEE6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE5D532-47F1-4C0B-A6E9-7030C652C813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
   <sheets>
     <sheet name="TestTS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>employeeID</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>3d54dcc7-9457-4dce-9a2f-ee9be4cc87db</t>
+  </si>
+  <si>
+    <t>52d770d7-1ea2-4ee4-afd1-ef2218d52948</t>
+  </si>
+  <si>
+    <t>d8f622c0-df5a-4130-92fb-cad96e4e1f97</t>
+  </si>
+  <si>
+    <t>2026-05-27T00:00:01</t>
+  </si>
+  <si>
+    <t>2026-05-28T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -451,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D3DF93-7FF5-4627-8449-A806EF56857A}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -491,7 +503,41 @@
         <v>5</v>
       </c>
       <c r="F2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE5D532-47F1-4C0B-A6E9-7030C652C813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAC6E4A-3783-4110-A4E7-A4BDF8CDEFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
+    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="9960" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
   <sheets>
     <sheet name="TestTS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>employeeID</t>
   </si>
@@ -74,10 +74,16 @@
     <t>d8f622c0-df5a-4130-92fb-cad96e4e1f97</t>
   </si>
   <si>
-    <t>2026-05-27T00:00:01</t>
-  </si>
-  <si>
     <t>2026-05-28T00:00:00</t>
+  </si>
+  <si>
+    <t>efeb568f-40c5-4f64-bd08-85e716f123a1</t>
+  </si>
+  <si>
+    <t>11acd8c6-00e6-4844-ba98-8b86e6081fe7</t>
+  </si>
+  <si>
+    <t>2026-05-27T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -514,10 +520,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -531,10 +537,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <v>10</v>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAC6E4A-3783-4110-A4E7-A4BDF8CDEFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81349484-7FA3-49E8-A1F8-C552CDB2E521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="9960" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="9960" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
   <sheets>
     <sheet name="TestTS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>employeeID</t>
   </si>
@@ -65,25 +65,7 @@
     <t>Weekly</t>
   </si>
   <si>
-    <t>3d54dcc7-9457-4dce-9a2f-ee9be4cc87db</t>
-  </si>
-  <si>
-    <t>52d770d7-1ea2-4ee4-afd1-ef2218d52948</t>
-  </si>
-  <si>
-    <t>d8f622c0-df5a-4130-92fb-cad96e4e1f97</t>
-  </si>
-  <si>
-    <t>2026-05-28T00:00:00</t>
-  </si>
-  <si>
     <t>efeb568f-40c5-4f64-bd08-85e716f123a1</t>
-  </si>
-  <si>
-    <t>11acd8c6-00e6-4844-ba98-8b86e6081fe7</t>
-  </si>
-  <si>
-    <t>2026-05-27T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -469,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D3DF93-7FF5-4627-8449-A806EF56857A}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -512,40 +494,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81349484-7FA3-49E8-A1F8-C552CDB2E521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF6C36B-9869-4950-8795-0F3A4A8FB4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="9960" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
   <sheets>
     <sheet name="TestTS" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>Weekly</t>
   </si>
   <si>
-    <t>efeb568f-40c5-4f64-bd08-85e716f123a1</t>
+    <t>11acd8c6-00e6-4844-ba98-8b86e6081fe7</t>
   </si>
 </sst>
 </file>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF6C36B-9869-4950-8795-0F3A4A8FB4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C636F0E1-738D-41B6-B7C1-B4A18AE67FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -491,7 +491,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C636F0E1-738D-41B6-B7C1-B4A18AE67FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3718A2-24B7-4497-9045-BA4619FF93EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Weekly</t>
   </si>
   <si>
-    <t>11acd8c6-00e6-4844-ba98-8b86e6081fe7</t>
+    <t>3747f42a-4cda-40c6-8e8f-896cd931f557</t>
   </si>
 </sst>
 </file>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3718A2-24B7-4497-9045-BA4619FF93EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDBF154-2EAE-4216-9F49-08497300666A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Weekly</t>
   </si>
   <si>
-    <t>3747f42a-4cda-40c6-8e8f-896cd931f557</t>
+    <t>11acd8c6-00e6-4844-ba98-8b86e6081fe7</t>
   </si>
 </sst>
 </file>

--- a/TestTS.xlsx
+++ b/TestTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csun\PycharmProjects\xerotimesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDBF154-2EAE-4216-9F49-08497300666A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249A68F7-6E9A-4590-A595-245576ADE1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A99D997A-F936-40B1-AEEF-33B6DA4524BA}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Weekly</t>
   </si>
   <si>
-    <t>11acd8c6-00e6-4844-ba98-8b86e6081fe7</t>
+    <t>e5d80793-5b30-401d-a278-6d782e086a00</t>
   </si>
 </sst>
 </file>
